--- a/ML-Entrees/ig/StructureDefinition-fr-cda-dicom-examen-comparatif.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-dicom-examen-comparatif.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:31:26+00:00</t>
+    <t>2026-04-24T12:30:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-cda-dicom-examen-comparatif.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-cda-dicom-examen-comparatif.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T12:30:57+00:00</t>
+    <t>2026-04-24T12:43:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
